--- a/data/trans_camb/P16A02-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A02-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 8,91</t>
+          <t>-3,6; 9,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 14,44</t>
+          <t>1,19; 14,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,35; 23,37</t>
+          <t>7,63; 22,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 15,05</t>
+          <t>0,42; 14,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,42; 22,41</t>
+          <t>8,05; 22,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,01; 32,78</t>
+          <t>19,01; 32,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 9,82</t>
+          <t>0,52; 10,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 16,42</t>
+          <t>6,02; 16,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,13; 25,37</t>
+          <t>15,56; 25,26</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 85,27</t>
+          <t>-21,83; 89,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 135,07</t>
+          <t>4,99; 133,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48,04; 221,28</t>
+          <t>39,41; 205,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 101,6</t>
+          <t>0,92; 98,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,82; 147,61</t>
+          <t>32,14; 157,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,57; 223,05</t>
+          <t>80,86; 219,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 70,45</t>
+          <t>2,19; 75,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,16; 117,31</t>
+          <t>33,44; 119,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>80,57; 189,03</t>
+          <t>82,94; 184,28</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 16,68</t>
+          <t>6,42; 16,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 11,98</t>
+          <t>3,19; 11,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,46; 18,55</t>
+          <t>8,74; 18,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 18,01</t>
+          <t>6,83; 18,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 13,16</t>
+          <t>2,11; 13,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,87; 23,51</t>
+          <t>13,25; 23,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,11; 15,86</t>
+          <t>8,01; 15,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 11,25</t>
+          <t>4,05; 11,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,98; 19,42</t>
+          <t>11,8; 19,69</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,94; 221,45</t>
+          <t>56,09; 221,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,34; 162,93</t>
+          <t>25,64; 151,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,71; 241,38</t>
+          <t>72,28; 242,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,36; 90,26</t>
+          <t>28,04; 92,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,82; 68,31</t>
+          <t>8,12; 67,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,65; 119,89</t>
+          <t>53,55; 119,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,58; 112,12</t>
+          <t>45,19; 107,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,76; 77,95</t>
+          <t>22,28; 77,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67,01; 133,84</t>
+          <t>67,18; 135,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 17,18</t>
+          <t>5,61; 17,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 14,3</t>
+          <t>3,42; 13,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,49; 23,51</t>
+          <t>12,0; 24,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 10,94</t>
+          <t>-2,99; 11,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 11,76</t>
+          <t>-2,93; 11,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,78; 19,88</t>
+          <t>6,72; 20,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 11,82</t>
+          <t>3,38; 12,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 11,26</t>
+          <t>2,11; 10,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,95; 20,32</t>
+          <t>11,11; 20,14</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41,36; 203,25</t>
+          <t>41,25; 201,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,37; 170,39</t>
+          <t>24,42; 170,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94,37; 282,03</t>
+          <t>86,89; 280,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 43,23</t>
+          <t>-9,4; 47,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 46,12</t>
+          <t>-8,47; 45,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,13; 79,0</t>
+          <t>20,82; 80,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,76; 66,69</t>
+          <t>15,19; 67,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,42; 63,1</t>
+          <t>9,55; 61,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>47,61; 114,55</t>
+          <t>50,57; 113,99</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 10,91</t>
+          <t>-0,99; 10,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,54; 19,32</t>
+          <t>7,64; 19,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,91; 23,08</t>
+          <t>8,68; 23,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,1; 24,86</t>
+          <t>11,45; 24,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,47; 30,26</t>
+          <t>16,35; 29,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 22,55</t>
+          <t>-2,43; 22,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,07; 15,94</t>
+          <t>7,11; 16,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,83; 23,2</t>
+          <t>13,71; 23,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,07; 20,77</t>
+          <t>4,06; 20,23</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 89,49</t>
+          <t>-6,92; 86,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42,64; 158,22</t>
+          <t>44,14; 158,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44,53; 187,39</t>
+          <t>49,11; 179,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46,05; 125,9</t>
+          <t>44,99; 128,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>63,7; 157,81</t>
+          <t>65,27; 154,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 110,53</t>
+          <t>-7,12; 107,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,38; 93,55</t>
+          <t>33,94; 97,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>66,62; 138,85</t>
+          <t>65,96; 138,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,25; 118,75</t>
+          <t>24,33; 115,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 9,16</t>
+          <t>-5,0; 10,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 6,42</t>
+          <t>-7,3; 6,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,96; 16,44</t>
+          <t>1,04; 15,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,51; 28,38</t>
+          <t>10,11; 28,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 13,15</t>
+          <t>-4,03; 12,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,24; 21,12</t>
+          <t>6,37; 21,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,14; 17,92</t>
+          <t>5,52; 17,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 7,92</t>
+          <t>-2,63; 8,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,91; 17,35</t>
+          <t>6,81; 17,25</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 81,91</t>
+          <t>-27,42; 99,24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,51; 59,94</t>
+          <t>-41,48; 57,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9,44; 153,95</t>
+          <t>4,37; 144,32</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33,26; 133,65</t>
+          <t>33,02; 138,43</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 64,45</t>
+          <t>-14,05; 62,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,89; 102,75</t>
+          <t>20,95; 105,21</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,51; 104,63</t>
+          <t>25,18; 103,66</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 48,2</t>
+          <t>-12,22; 46,48</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>30,87; 104,68</t>
+          <t>28,84; 104,31</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,27; 12,11</t>
+          <t>-0,24; 11,84</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 8,15</t>
+          <t>-5,07; 7,14</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9,52; 21,99</t>
+          <t>9,41; 22,05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,52; 20,85</t>
+          <t>5,71; 21,25</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 7,94</t>
+          <t>-6,69; 8,62</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,73; 25,62</t>
+          <t>11,1; 25,85</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,46; 14,71</t>
+          <t>4,53; 14,52</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 5,79</t>
+          <t>-4,07; 6,04</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11,92; 21,08</t>
+          <t>11,92; 21,61</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1,28; 113,1</t>
+          <t>-1,64; 110,33</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-27,44; 71,84</t>
+          <t>-31,88; 64,77</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>53,91; 202,27</t>
+          <t>52,78; 204,58</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19,03; 102,79</t>
+          <t>19,43; 105,01</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 37,46</t>
+          <t>-24,27; 40,26</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>36,43; 126,28</t>
+          <t>38,13; 127,49</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,78; 87,16</t>
+          <t>21,43; 85,09</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 33,93</t>
+          <t>-18,91; 35,93</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>55,35; 128,27</t>
+          <t>52,57; 128,35</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 7,0</t>
+          <t>-1,28; 7,35</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 5,26</t>
+          <t>-3,18; 4,5</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7,64; 17,52</t>
+          <t>7,8; 17,9</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,47; 16,29</t>
+          <t>6,52; 16,17</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 5,84</t>
+          <t>-3,19; 5,67</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,5; 54,72</t>
+          <t>18,61; 58,06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,9; 10,44</t>
+          <t>4,23; 10,74</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 4,25</t>
+          <t>-1,92; 4,18</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15,33; 48,96</t>
+          <t>15,13; 45,32</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 55,98</t>
+          <t>-7,9; 59,12</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 45,81</t>
+          <t>-19,45; 36,85</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>46,26; 142,92</t>
+          <t>47,44; 144,5</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>28,1; 89,56</t>
+          <t>27,98; 86,72</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 31,42</t>
+          <t>-13,7; 30,18</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>85,69; 284,41</t>
+          <t>85,91; 336,59</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,34; 65,13</t>
+          <t>21,97; 68,61</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 26,89</t>
+          <t>-10,13; 26,95</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>83,99; 299,86</t>
+          <t>83,62; 276,59</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 0,32</t>
+          <t>-7,3; 0,19</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 6,22</t>
+          <t>-1,73; 6,32</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-13,66; -2,45</t>
+          <t>-14,79; -2,49</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 6,6</t>
+          <t>-2,78; 6,33</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,45</t>
+          <t>1,44; 10,57</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 8,15</t>
+          <t>-0,43; 8,34</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 2,02</t>
+          <t>-3,57; 2,44</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,4</t>
+          <t>1,28; 7,22</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 0,99</t>
+          <t>-10,92; 1,12</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-37,74; 2,76</t>
+          <t>-36,85; 2,26</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 38,76</t>
+          <t>-8,96; 39,86</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-75,12; -15,15</t>
+          <t>-73,72; -15,26</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 26,81</t>
+          <t>-9,26; 25,9</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,82; 42,42</t>
+          <t>5,08; 42,68</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 33,36</t>
+          <t>-1,27; 34,0</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 9,73</t>
+          <t>-14,93; 11,6</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>4,74; 35,66</t>
+          <t>5,33; 34,23</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 4,52</t>
+          <t>-47,26; 5,1</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,74</t>
+          <t>2,18; 5,96</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,7</t>
+          <t>3,12; 6,8</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3,74; 11,11</t>
+          <t>2,87; 11,23</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7,53; 11,72</t>
+          <t>7,61; 11,95</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>5,0; 9,19</t>
+          <t>5,14; 9,51</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,82; 29,23</t>
+          <t>13,41; 27,81</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,21</t>
+          <t>5,43; 8,31</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,63</t>
+          <t>4,7; 7,62</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>10,07; 20,12</t>
+          <t>10,04; 19,45</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>14,09; 43,93</t>
+          <t>14,62; 45,72</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>21,14; 50,37</t>
+          <t>20,98; 51,52</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>27,65; 84,54</t>
+          <t>22,65; 84,33</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>30,33; 50,89</t>
+          <t>30,47; 53,22</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>20,12; 40,06</t>
+          <t>20,29; 41,24</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>56,71; 123,79</t>
+          <t>55,0; 116,79</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>26,83; 45,22</t>
+          <t>27,83; 45,4</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>24,07; 41,73</t>
+          <t>23,57; 41,77</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>52,09; 105,95</t>
+          <t>50,89; 102,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A02-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A02-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,45</t>
+          <t>16,08</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,68</t>
+          <t>24,75</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20,35</t>
+          <t>20,44</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 9,63</t>
+          <t>-2,23; 9,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 14,25</t>
+          <t>1,01; 14,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 22,79</t>
+          <t>9,36; 22,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 14,61</t>
+          <t>0,68; 14,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,05; 22,87</t>
+          <t>7,23; 22,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,01; 32,6</t>
+          <t>17,41; 31,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 10,21</t>
+          <t>0,69; 10,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,02; 16,66</t>
+          <t>6,2; 16,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,56; 25,26</t>
+          <t>15,52; 25,37</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>112,43%</t>
+          <t>117,02%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>140,47%</t>
+          <t>135,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>127,5%</t>
+          <t>128,06%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,83; 89,68</t>
+          <t>-15,36; 88,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,99; 133,9</t>
+          <t>2,92; 126,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,41; 205,12</t>
+          <t>48,14; 208,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 98,38</t>
+          <t>3,18; 102,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,14; 157,96</t>
+          <t>31,35; 147,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,86; 219,72</t>
+          <t>74,68; 211,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 75,43</t>
+          <t>3,9; 77,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,44; 119,06</t>
+          <t>33,98; 123,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82,94; 184,28</t>
+          <t>83,88; 190,72</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,57</t>
+          <t>13,67</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,43</t>
+          <t>17,73</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15,9</t>
+          <t>15,75</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 16,2</t>
+          <t>7,33; 15,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 11,59</t>
+          <t>3,34; 11,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,74; 18,71</t>
+          <t>8,58; 18,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 18,13</t>
+          <t>7,17; 18,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 13,38</t>
+          <t>2,22; 13,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,25; 23,22</t>
+          <t>12,61; 22,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,01; 15,63</t>
+          <t>8,32; 15,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 11,11</t>
+          <t>4,12; 11,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,8; 19,69</t>
+          <t>11,79; 19,66</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142,38%</t>
+          <t>143,45%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56,09; 221,71</t>
+          <t>60,44; 211,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,64; 151,24</t>
+          <t>28,04; 150,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,28; 242,0</t>
+          <t>70,66; 237,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,04; 92,02</t>
+          <t>27,75; 94,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,12; 67,86</t>
+          <t>8,14; 68,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,55; 119,46</t>
+          <t>48,74; 117,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,19; 107,3</t>
+          <t>47,07; 111,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,28; 77,29</t>
+          <t>23,06; 79,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67,18; 135,46</t>
+          <t>65,52; 137,31</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17,81</t>
+          <t>18,46</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,4</t>
+          <t>14,02</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15,71</t>
+          <t>16,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,61; 17,04</t>
+          <t>5,84; 17,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 13,91</t>
+          <t>2,96; 13,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,0; 24,1</t>
+          <t>12,65; 24,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 11,8</t>
+          <t>-4,12; 10,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 11,34</t>
+          <t>-2,63; 11,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,72; 20,06</t>
+          <t>7,89; 20,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,38; 12,31</t>
+          <t>2,98; 12,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 10,8</t>
+          <t>2,03; 11,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,11; 20,14</t>
+          <t>11,65; 20,63</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164,69%</t>
+          <t>170,7%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41,25; 201,32</t>
+          <t>42,79; 206,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,42; 170,78</t>
+          <t>22,77; 161,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,89; 280,17</t>
+          <t>89,5; 289,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 47,58</t>
+          <t>-12,6; 41,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 45,95</t>
+          <t>-9,58; 46,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,82; 80,15</t>
+          <t>24,33; 85,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,19; 67,08</t>
+          <t>13,37; 68,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,55; 61,36</t>
+          <t>8,93; 62,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50,57; 113,99</t>
+          <t>52,13; 118,35</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15,53</t>
+          <t>14,47</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,54</t>
+          <t>21,05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14,44</t>
+          <t>18,13</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 10,45</t>
+          <t>-1,19; 10,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,64; 19,66</t>
+          <t>7,61; 19,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,68; 23,33</t>
+          <t>7,86; 21,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,45; 24,53</t>
+          <t>11,53; 24,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,35; 29,78</t>
+          <t>16,85; 30,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 22,38</t>
+          <t>14,8; 27,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,11; 16,22</t>
+          <t>7,11; 16,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,71; 23,14</t>
+          <t>14,1; 23,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,06; 20,23</t>
+          <t>13,25; 22,79</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>104,17%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 86,28</t>
+          <t>-8,04; 83,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>44,14; 158,55</t>
+          <t>40,36; 159,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49,11; 179,81</t>
+          <t>42,48; 172,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44,99; 128,99</t>
+          <t>45,12; 127,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>65,27; 154,41</t>
+          <t>63,92; 163,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 107,19</t>
+          <t>57,21; 141,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,94; 97,02</t>
+          <t>34,2; 97,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>65,96; 138,86</t>
+          <t>67,46; 140,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24,33; 115,92</t>
+          <t>63,18; 135,73</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8,92</t>
+          <t>7,51</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,1</t>
+          <t>12,45</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12,08</t>
+          <t>10,32</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 10,6</t>
+          <t>-4,83; 9,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 6,21</t>
+          <t>-7,19; 6,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,04; 15,47</t>
+          <t>0,51; 14,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,11; 28,02</t>
+          <t>9,75; 27,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 12,95</t>
+          <t>-4,59; 13,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,37; 21,27</t>
+          <t>4,87; 20,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,52; 17,15</t>
+          <t>4,93; 17,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 8,1</t>
+          <t>-3,34; 7,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,81; 17,25</t>
+          <t>5,0; 14,79</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 99,24</t>
+          <t>-26,81; 82,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,48; 57,62</t>
+          <t>-40,66; 61,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4,37; 144,32</t>
+          <t>2,08; 131,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33,02; 138,43</t>
+          <t>30,49; 126,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 62,17</t>
+          <t>-15,31; 63,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,95; 105,21</t>
+          <t>15,71; 99,32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,18; 103,66</t>
+          <t>20,44; 106,01</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 46,48</t>
+          <t>-14,71; 49,0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>28,84; 104,31</t>
+          <t>21,86; 87,11</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15,81</t>
+          <t>15,0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,35</t>
+          <t>18,26</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16,84</t>
+          <t>16,46</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 11,84</t>
+          <t>-0,79; 11,83</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 7,14</t>
+          <t>-4,53; 7,48</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9,41; 22,05</t>
+          <t>8,74; 20,4</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,71; 21,25</t>
+          <t>5,71; 20,62</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 8,62</t>
+          <t>-6,54; 8,14</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,1; 25,85</t>
+          <t>10,44; 24,77</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,53; 14,52</t>
+          <t>4,78; 15,4</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 6,04</t>
+          <t>-3,35; 6,56</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11,92; 21,61</t>
+          <t>11,49; 21,25</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>117,59%</t>
+          <t>111,59%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 110,33</t>
+          <t>-6,38; 108,91</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-31,88; 64,77</t>
+          <t>-27,93; 68,46</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>52,78; 204,58</t>
+          <t>49,88; 185,52</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19,43; 105,01</t>
+          <t>20,09; 96,76</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 40,26</t>
+          <t>-23,03; 40,48</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>38,13; 127,49</t>
+          <t>37,16; 117,72</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,43; 85,09</t>
+          <t>22,09; 91,08</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 35,93</t>
+          <t>-15,82; 38,94</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>52,57; 128,35</t>
+          <t>52,53; 133,08</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12,52</t>
+          <t>12,53</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,37</t>
+          <t>19,82</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>25,57</t>
+          <t>16,36</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 7,35</t>
+          <t>-1,11; 7,22</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 4,5</t>
+          <t>-3,23; 5,17</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7,8; 17,9</t>
+          <t>8,22; 17,83</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,52; 16,17</t>
+          <t>6,51; 16,47</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 5,67</t>
+          <t>-3,2; 5,94</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,61; 58,06</t>
+          <t>15,41; 24,18</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,23; 10,74</t>
+          <t>4,06; 10,73</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,18</t>
+          <t>-2,34; 4,04</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15,13; 45,32</t>
+          <t>12,72; 19,59</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>164,56%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>145,68%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 59,12</t>
+          <t>-7,4; 57,35</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 36,85</t>
+          <t>-20,16; 42,95</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>47,44; 144,5</t>
+          <t>50,35; 146,68</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27,98; 86,72</t>
+          <t>27,98; 88,18</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 30,18</t>
+          <t>-13,8; 33,37</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>85,91; 336,59</t>
+          <t>65,66; 133,62</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,97; 68,61</t>
+          <t>21,16; 68,79</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 26,95</t>
+          <t>-11,79; 25,15</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>83,62; 276,59</t>
+          <t>64,27; 121,73</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-7,55</t>
+          <t>-4,43</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>3,12</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-3,29</t>
+          <t>-0,62</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 0,19</t>
+          <t>-7,21; -0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 6,32</t>
+          <t>-1,82; 6,32</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-14,79; -2,49</t>
+          <t>-8,07; -0,73</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 6,33</t>
+          <t>-2,73; 6,05</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,44; 10,57</t>
+          <t>1,57; 10,73</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 8,34</t>
+          <t>-1,35; 7,29</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 2,44</t>
+          <t>-3,68; 2,45</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,22</t>
+          <t>0,78; 7,39</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 1,12</t>
+          <t>-3,44; 2,35</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-42,64%</t>
+          <t>-25,06%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-14,56%</t>
+          <t>-2,73%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-36,85; 2,26</t>
+          <t>-36,67; 0,36</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 39,86</t>
+          <t>-9,45; 39,18</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-73,72; -15,26</t>
+          <t>-40,32; -3,96</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 25,9</t>
+          <t>-9,35; 23,87</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,08; 42,68</t>
+          <t>4,94; 43,0</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 34,0</t>
+          <t>-4,69; 29,91</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 11,6</t>
+          <t>-15,63; 11,78</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>5,33; 34,23</t>
+          <t>3,08; 35,17</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-47,26; 5,1</t>
+          <t>-14,07; 11,09</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8,54</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,07</t>
+          <t>15,09</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>13,5</t>
+          <t>12,6</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,96</t>
+          <t>2,13; 5,82</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,8</t>
+          <t>3,32; 6,78</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2,87; 11,23</t>
+          <t>7,87; 12,01</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7,61; 11,95</t>
+          <t>7,47; 12,01</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>5,14; 9,51</t>
+          <t>5,04; 9,4</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,41; 27,81</t>
+          <t>13,09; 17,07</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,31</t>
+          <t>5,36; 8,26</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>4,7; 7,62</t>
+          <t>4,73; 7,64</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>10,04; 19,45</t>
+          <t>11,32; 14,12</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>66,42%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>14,62; 45,72</t>
+          <t>14,67; 44,85</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>20,98; 51,52</t>
+          <t>22,1; 50,77</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>22,65; 84,33</t>
+          <t>54,15; 92,18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>30,47; 53,22</t>
+          <t>29,9; 53,08</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>20,29; 41,24</t>
+          <t>20,26; 41,64</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>55,0; 116,79</t>
+          <t>52,58; 75,6</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>27,83; 45,4</t>
+          <t>27,44; 45,23</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>23,57; 41,77</t>
+          <t>23,71; 41,64</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>50,89; 102,13</t>
+          <t>57,45; 77,62</t>
         </is>
       </c>
     </row>
